--- a/GameDesign/Excel/Localization/Loc_Character.xlsx
+++ b/GameDesign/Excel/Localization/Loc_Character.xlsx
@@ -530,7 +530,7 @@
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
   </cols>
@@ -666,12 +666,12 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>램볼</t>
+          <t>떠돌이 전사</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Lambol</t>
+          <t>Wandering Warrior</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr"/>
@@ -685,12 +685,12 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>치키피</t>
+          <t>숲 슬라임</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Chickipee</t>
+          <t>Forest Slime</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>펭구렛</t>
+          <t>뿔쥐</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Pengulet</t>
+          <t>Horned Rat</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr"/>
@@ -723,12 +723,12 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>캐티바</t>
+          <t>가시 슬라임</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Kattiva</t>
+          <t>Spiked Slime</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr"/>
@@ -742,12 +742,12 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>리프몽</t>
+          <t>방랑 기사</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Leafmong</t>
+          <t>Errant Knight</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr"/>
@@ -761,12 +761,12 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>폭스파크스</t>
+          <t>날개 눈알</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>Foxparks</t>
+          <t>Flying Eye</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr"/>
@@ -780,12 +780,12 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>밀개비</t>
+          <t>들쥐</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Wheatbird</t>
+          <t>Field Rat</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr"/>
@@ -818,12 +818,12 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>두더삽</t>
+          <t>동굴 박쥐</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Molespade</t>
+          <t>Cave Bat</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr"/>
@@ -856,12 +856,12 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>살쾡이</t>
+          <t>흡혈 박쥐</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>Wildcat</t>
+          <t>Vampire Bat</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr"/>
@@ -875,12 +875,12 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>갈대오리</t>
+          <t>망령 마법사</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>Reed Duck</t>
+          <t>Wraith Mage</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr"/>
@@ -894,12 +894,12 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>뿔사슴이</t>
+          <t>화염 마법사</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>Hornstag</t>
+          <t>Fire Wizard</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr"/>
@@ -932,12 +932,12 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>해달수</t>
+          <t>미믹</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Sea Otter</t>
+          <t>Mimic</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr"/>
@@ -951,12 +951,12 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>흙두꺼비</t>
+          <t>버섯 인간</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>Mud Toad</t>
+          <t>Mushroom Folk</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr"/>
@@ -970,12 +970,12 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>광부오소리</t>
+          <t>고블린</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Miner Badger</t>
+          <t>Goblin</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr"/>
@@ -989,12 +989,12 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>도끼늑대</t>
+          <t>은빛 기사</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>Axe Wolf</t>
+          <t>Silver Knight</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr"/>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>창날매</t>
+          <t>그림자 마법사</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Spearhawk</t>
+          <t>Shadow Wizard</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr"/>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>이삭토끼</t>
+          <t>무예가</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>Ear-of-Grain Bunny</t>
+          <t>Martial Hero</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr"/>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>산호게</t>
+          <t>해골 병사</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>Coral Crab</t>
+          <t>Skeleton Soldier</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr"/>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>화산도롱뇽</t>
+          <t>바위 골렘</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>Volcano Salamander</t>
+          <t>Stone Golem</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr"/>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>파도고래</t>
+          <t>붉은 집게게</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Wave Whale</t>
+          <t>Red Crab</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr"/>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>대지곰</t>
+          <t>대검 전사</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>Earth Bear</t>
+          <t>Greatsword Warrior</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr"/>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>강철사마귀</t>
+          <t>검왕</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Steel Mantis</t>
+          <t>Sword King</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr"/>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>거목정령</t>
+          <t>영웅 기사</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>Great Tree Spirit</t>
+          <t>Hero Knight</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr"/>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>황금기린</t>
+          <t>죽음의 사신</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Golden Giraffe</t>
+          <t>Bringer of Death</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr"/>
@@ -1179,12 +1179,12 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>심연이무기</t>
+          <t>흑기사</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Abyss Serpent</t>
+          <t>Black Knight</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr"/>
@@ -1217,12 +1217,12 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>별빛드래곤</t>
+          <t>질풍 검호</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>Starlight Dragon</t>
+          <t>Gale Swordmaster</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr"/>

--- a/GameDesign/Excel/Localization/Loc_Character.xlsx
+++ b/GameDesign/Excel/Localization/Loc_Character.xlsx
@@ -88,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -159,6 +159,18 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -526,12 +538,12 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E36"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.139196" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.210625" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -548,22 +560,22 @@
           <t>//</t>
         </is>
       </c>
-      <c r="B2" s="22" t="inlineStr">
+      <c r="B2" s="25" t="inlineStr">
         <is>
           <t>키</t>
         </is>
       </c>
-      <c r="C2" s="22" t="inlineStr">
+      <c r="C2" s="25" t="inlineStr">
         <is>
           <t>한국어(원문)</t>
         </is>
       </c>
-      <c r="D2" s="22" t="inlineStr">
+      <c r="D2" s="25" t="inlineStr">
         <is>
           <t>영어</t>
         </is>
       </c>
-      <c r="E2" s="22" t="inlineStr">
+      <c r="E2" s="25" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
@@ -575,22 +587,22 @@
           <t>C&amp;S</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="26" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="C3" s="23" t="inlineStr">
+      <c r="C3" s="26" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="D3" s="23" t="inlineStr">
+      <c r="D3" s="26" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="E3" s="23" t="n"/>
+      <c r="E3" s="26" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -598,22 +610,22 @@
           <t>Type</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="26" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
+      <c r="C4" s="26" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D4" s="23" t="inlineStr">
+      <c r="D4" s="26" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E4" s="23" t="n"/>
+      <c r="E4" s="26" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -621,37 +633,37 @@
           <t>Default(Null)</t>
         </is>
       </c>
-      <c r="B5" s="23" t="n"/>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>""</t>
         </is>
       </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D5" s="26" t="inlineStr">
         <is>
           <t>""</t>
         </is>
       </c>
-      <c r="E5" s="23" t="n"/>
+      <c r="E5" s="26" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="27" t="inlineStr">
         <is>
           <t>Key</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="27" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="E6" s="24" t="inlineStr">
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -674,7 +686,7 @@
           <t>Wandering Warrior</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr"/>
+      <c r="E7" s="28" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -693,7 +705,7 @@
           <t>Forest Slime</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr"/>
+      <c r="E8" s="28" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -712,7 +724,7 @@
           <t>Horned Rat</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr"/>
+      <c r="E9" s="28" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n"/>
@@ -731,7 +743,7 @@
           <t>Spiked Slime</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr"/>
+      <c r="E10" s="28" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -750,7 +762,7 @@
           <t>Errant Knight</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr"/>
+      <c r="E11" s="28" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -769,7 +781,7 @@
           <t>Flying Eye</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr"/>
+      <c r="E12" s="28" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,7 +800,7 @@
           <t>Field Rat</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr"/>
+      <c r="E13" s="28" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -799,15 +811,15 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>물방개미</t>
+          <t>견습 발굴꾼</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>Diving Beetle</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr"/>
+          <t>Apprentice Digger</t>
+        </is>
+      </c>
+      <c r="E14" s="28" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -826,7 +838,7 @@
           <t>Cave Bat</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr"/>
+      <c r="E15" s="28" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n"/>
@@ -837,15 +849,15 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>톱니쥐</t>
+          <t>견습 나무꾼</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>Gearmouse</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr"/>
+          <t>Apprentice Woodcutter</t>
+        </is>
+      </c>
+      <c r="E16" s="28" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -864,7 +876,7 @@
           <t>Vampire Bat</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr"/>
+      <c r="E17" s="28" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -883,7 +895,7 @@
           <t>Wraith Mage</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr"/>
+      <c r="E18" s="28" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -902,7 +914,7 @@
           <t>Fire Wizard</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr"/>
+      <c r="E19" s="28" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -913,15 +925,15 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>솔방울곰</t>
+          <t>나무꾼</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>Pinecone Bear</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr"/>
+          <t>Woodcutter</t>
+        </is>
+      </c>
+      <c r="E20" s="28" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -940,7 +952,7 @@
           <t>Mimic</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr"/>
+      <c r="E21" s="28" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n"/>
@@ -959,7 +971,7 @@
           <t>Mushroom Folk</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr"/>
+      <c r="E22" s="28" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -978,7 +990,7 @@
           <t>Goblin</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr"/>
+      <c r="E23" s="28" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -997,7 +1009,7 @@
           <t>Silver Knight</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr"/>
+      <c r="E24" s="28" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1016,7 +1028,7 @@
           <t>Shadow Wizard</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr"/>
+      <c r="E25" s="28" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1035,7 +1047,7 @@
           <t>Martial Hero</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr"/>
+      <c r="E26" s="28" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1054,7 +1066,7 @@
           <t>Skeleton Soldier</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr"/>
+      <c r="E27" s="28" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n"/>
@@ -1073,7 +1085,7 @@
           <t>Stone Golem</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr"/>
+      <c r="E28" s="28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1092,7 +1104,7 @@
           <t>Red Crab</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr"/>
+      <c r="E29" s="28" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1111,7 +1123,7 @@
           <t>Greatsword Warrior</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr"/>
+      <c r="E30" s="28" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1130,7 +1142,7 @@
           <t>Sword King</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr"/>
+      <c r="E31" s="28" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1149,7 +1161,7 @@
           <t>Hero Knight</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr"/>
+      <c r="E32" s="28" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1168,7 +1180,7 @@
           <t>Bringer of Death</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr"/>
+      <c r="E33" s="28" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n"/>
@@ -1187,7 +1199,7 @@
           <t>Black Knight</t>
         </is>
       </c>
-      <c r="E34" s="6" t="inlineStr"/>
+      <c r="E34" s="28" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n"/>
@@ -1206,7 +1218,7 @@
           <t>Obsidian Golem</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr"/>
+      <c r="E35" s="28" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n"/>
@@ -1225,7 +1237,7 @@
           <t>Gale Swordmaster</t>
         </is>
       </c>
-      <c r="E36" s="6" t="inlineStr"/>
+      <c r="E36" s="28" t="inlineStr"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>

--- a/GameDesign/Excel/Localization/Loc_Character.xlsx
+++ b/GameDesign/Excel/Localization/Loc_Character.xlsx
@@ -88,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -171,6 +171,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -537,8 +546,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.210625" defaultRowHeight="15"/>
+  <dimension ref="A1:E37"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.139196" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
@@ -547,697 +556,678 @@
     <col width="8" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="n"/>
-      <c r="B1" s="1" t="n"/>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-    </row>
+    <row r="1"/>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>//</t>
         </is>
       </c>
-      <c r="B2" s="25" t="inlineStr">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>키</t>
         </is>
       </c>
-      <c r="C2" s="25" t="inlineStr">
+      <c r="C2" s="29" t="inlineStr">
         <is>
           <t>한국어(원문)</t>
         </is>
       </c>
-      <c r="D2" s="25" t="inlineStr">
+      <c r="D2" s="29" t="inlineStr">
         <is>
           <t>영어</t>
         </is>
       </c>
-      <c r="E2" s="25" t="inlineStr">
+      <c r="E2" s="29" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>C&amp;S</t>
         </is>
       </c>
-      <c r="B3" s="26" t="inlineStr">
+      <c r="B3" s="30" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="C3" s="26" t="inlineStr">
+      <c r="C3" s="30" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="D3" s="26" t="inlineStr">
+      <c r="D3" s="30" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="E3" s="26" t="n"/>
+      <c r="E3" s="30" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B4" s="26" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C4" s="26" t="inlineStr">
+      <c r="C4" s="30" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D4" s="26" t="inlineStr">
+      <c r="D4" s="30" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E4" s="26" t="n"/>
+      <c r="E4" s="30" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Default(Null)</t>
         </is>
       </c>
-      <c r="B5" s="26" t="n"/>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="B5" s="30" t="n"/>
+      <c r="C5" s="30" t="inlineStr">
         <is>
           <t>""</t>
         </is>
       </c>
-      <c r="D5" s="26" t="inlineStr">
+      <c r="D5" s="30" t="inlineStr">
         <is>
           <t>""</t>
         </is>
       </c>
-      <c r="E5" s="26" t="n"/>
+      <c r="E5" s="30" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n"/>
-      <c r="B6" s="27" t="inlineStr">
+      <c r="B6" s="31" t="inlineStr">
         <is>
           <t>Key</t>
         </is>
       </c>
-      <c r="C6" s="27" t="inlineStr">
+      <c r="C6" s="31" t="inlineStr">
         <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="D6" s="27" t="inlineStr">
+      <c r="D6" s="31" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="E6" s="27" t="inlineStr">
+      <c r="E6" s="31" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Character.1001.Name</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>떠돌이 전사</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>Wandering Warrior</t>
         </is>
       </c>
-      <c r="E7" s="28" t="inlineStr"/>
+      <c r="E7" s="11" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n"/>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>Character.1002.Name</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>숲 슬라임</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>Forest Slime</t>
         </is>
       </c>
-      <c r="E8" s="28" t="inlineStr"/>
+      <c r="E8" s="11" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>Character.1003.Name</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>뿔쥐</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>Horned Rat</t>
         </is>
       </c>
-      <c r="E9" s="28" t="inlineStr"/>
+      <c r="E9" s="11" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n"/>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>Character.1004.Name</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>가시 슬라임</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>Spiked Slime</t>
         </is>
       </c>
-      <c r="E10" s="28" t="inlineStr"/>
+      <c r="E10" s="11" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>Character.1005.Name</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>방랑 기사</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>Errant Knight</t>
         </is>
       </c>
-      <c r="E11" s="28" t="inlineStr"/>
+      <c r="E11" s="11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n"/>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>Character.1006.Name</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>날개 눈알</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>Flying Eye</t>
         </is>
       </c>
-      <c r="E12" s="28" t="inlineStr"/>
+      <c r="E12" s="11" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Character.1007.Name</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>들쥐</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>Field Rat</t>
         </is>
       </c>
-      <c r="E13" s="28" t="inlineStr"/>
+      <c r="E13" s="11" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n"/>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>Character.1008.Name</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>견습 발굴꾼</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>Apprentice Digger</t>
         </is>
       </c>
-      <c r="E14" s="28" t="n"/>
+      <c r="E14" s="11" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n"/>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>Character.1009.Name</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>동굴 박쥐</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>Cave Bat</t>
         </is>
       </c>
-      <c r="E15" s="28" t="inlineStr"/>
+      <c r="E15" s="11" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n"/>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>Character.1010.Name</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>견습 나무꾼</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>Apprentice Woodcutter</t>
         </is>
       </c>
-      <c r="E16" s="28" t="n"/>
+      <c r="E16" s="11" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>Character.1011.Name</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>흡혈 박쥐</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>Vampire Bat</t>
         </is>
       </c>
-      <c r="E17" s="28" t="inlineStr"/>
+      <c r="E17" s="11" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n"/>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>Character.1012.Name</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>망령 마법사</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>Wraith Mage</t>
         </is>
       </c>
-      <c r="E18" s="28" t="inlineStr"/>
+      <c r="E18" s="11" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n"/>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>Character.1013.Name</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>화염 마법사</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>Fire Wizard</t>
         </is>
       </c>
-      <c r="E19" s="28" t="inlineStr"/>
+      <c r="E19" s="11" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n"/>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>Character.1014.Name</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>나무꾼</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="11" t="inlineStr">
         <is>
           <t>Woodcutter</t>
         </is>
       </c>
-      <c r="E20" s="28" t="n"/>
+      <c r="E20" s="11" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n"/>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>Character.1015.Name</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>미믹</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="11" t="inlineStr">
         <is>
           <t>Mimic</t>
         </is>
       </c>
-      <c r="E21" s="28" t="inlineStr"/>
+      <c r="E21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n"/>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>Character.1016.Name</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>버섯 인간</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>Mushroom Folk</t>
         </is>
       </c>
-      <c r="E22" s="28" t="inlineStr"/>
+      <c r="E22" s="11" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>Character.1017.Name</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>고블린</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="11" t="inlineStr">
         <is>
           <t>Goblin</t>
         </is>
       </c>
-      <c r="E23" s="28" t="inlineStr"/>
+      <c r="E23" s="11" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>Character.1018.Name</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>은빛 기사</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" s="11" t="inlineStr">
         <is>
           <t>Silver Knight</t>
         </is>
       </c>
-      <c r="E24" s="28" t="inlineStr"/>
+      <c r="E24" s="11" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n"/>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>Character.1019.Name</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>그림자 마법사</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" s="11" t="inlineStr">
         <is>
           <t>Shadow Wizard</t>
         </is>
       </c>
-      <c r="E25" s="28" t="inlineStr"/>
+      <c r="E25" s="11" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n"/>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>Character.1020.Name</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>무예가</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" s="11" t="inlineStr">
         <is>
           <t>Martial Hero</t>
         </is>
       </c>
-      <c r="E26" s="28" t="inlineStr"/>
+      <c r="E26" s="11" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n"/>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>Character.1021.Name</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C27" s="11" t="inlineStr">
         <is>
           <t>해골 병사</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" s="11" t="inlineStr">
         <is>
           <t>Skeleton Soldier</t>
         </is>
       </c>
-      <c r="E27" s="28" t="inlineStr"/>
+      <c r="E27" s="11" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n"/>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>Character.1022.Name</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C28" s="11" t="inlineStr">
         <is>
           <t>바위 골렘</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D28" s="11" t="inlineStr">
         <is>
           <t>Stone Golem</t>
         </is>
       </c>
-      <c r="E28" s="28" t="inlineStr"/>
+      <c r="E28" s="11" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n"/>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>Character.1023.Name</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C29" s="11" t="inlineStr">
         <is>
           <t>붉은 집게게</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D29" s="11" t="inlineStr">
         <is>
           <t>Red Crab</t>
         </is>
       </c>
-      <c r="E29" s="28" t="inlineStr"/>
+      <c r="E29" s="11" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n"/>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>Character.1024.Name</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C30" s="11" t="inlineStr">
         <is>
           <t>대검 전사</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D30" s="11" t="inlineStr">
         <is>
           <t>Greatsword Warrior</t>
         </is>
       </c>
-      <c r="E30" s="28" t="inlineStr"/>
+      <c r="E30" s="11" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n"/>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>Character.1025.Name</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C31" s="11" t="inlineStr">
         <is>
           <t>검왕</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D31" s="11" t="inlineStr">
         <is>
           <t>Sword King</t>
         </is>
       </c>
-      <c r="E31" s="28" t="inlineStr"/>
+      <c r="E31" s="11" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n"/>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>Character.1026.Name</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>영웅 기사</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D32" s="11" t="inlineStr">
         <is>
           <t>Hero Knight</t>
         </is>
       </c>
-      <c r="E32" s="28" t="inlineStr"/>
+      <c r="E32" s="11" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n"/>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>Character.1027.Name</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C33" s="11" t="inlineStr">
         <is>
           <t>죽음의 사신</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D33" s="11" t="inlineStr">
         <is>
           <t>Bringer of Death</t>
         </is>
       </c>
-      <c r="E33" s="28" t="inlineStr"/>
+      <c r="E33" s="11" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n"/>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t>Character.1028.Name</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C34" s="11" t="inlineStr">
         <is>
           <t>흑기사</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D34" s="11" t="inlineStr">
         <is>
           <t>Black Knight</t>
         </is>
       </c>
-      <c r="E34" s="28" t="inlineStr"/>
+      <c r="E34" s="11" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n"/>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t>Character.1029.Name</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C35" s="11" t="inlineStr">
         <is>
           <t>흑요석골렘</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D35" s="11" t="inlineStr">
         <is>
           <t>Obsidian Golem</t>
         </is>
       </c>
-      <c r="E35" s="28" t="inlineStr"/>
+      <c r="E35" s="11" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n"/>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B36" s="11" t="inlineStr">
         <is>
           <t>Character.1030.Name</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C36" s="11" t="inlineStr">
         <is>
           <t>질풍 검호</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D36" s="11" t="inlineStr">
         <is>
           <t>Gale Swordmaster</t>
         </is>
       </c>
-      <c r="E36" s="28" t="inlineStr"/>
+      <c r="E36" s="11" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>Character.1031.Name</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>숙련 채굴꾼</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>Skilled Miner</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
